--- a/Example/【必读】例程功能说明.xlsx
+++ b/Example/【必读】例程功能说明.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC114CB-8EAA-4DC8-B26D-56E151B09314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B774855-DE73-452F-BBF5-3C1F968DB65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="31196" windowHeight="17038" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="253">
   <si>
     <t>文件夹名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -864,26 +864,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E03_编码器部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E02_电机驱动与舵机部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E05_姿态传感器部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>oled_display_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E06_显示模块部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tft180_display_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -932,10 +916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E07_无线传输模块部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bluetooth_ch9141_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -980,10 +960,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E08_定位与测距模块部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>gps_tau1201_pc_mono_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1004,10 +980,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E09_图像传感器模块部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ov7725_wireless_uart_pc_mono_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1077,6 +1049,30 @@
   </si>
   <si>
     <t>文件系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E03_电机驱动与舵机部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E04_姿态传感器部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E05_显示模块部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E06_无线传输模块部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E07_定位与测距模块部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E08_图像传感器模块部分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1343,12 +1339,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1385,8 +1377,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1749,240 +1745,240 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="19" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="19" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="19" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="19" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="19" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="19" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="19" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="19" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="19" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="D18" s="33" t="s">
+      <c r="C18" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="19" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="19" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="19" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="19" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2008,11 +2004,11 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
     </row>
     <row r="28" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
@@ -2029,16 +2025,16 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="18" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2057,11 +2053,11 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
     </row>
     <row r="32" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
@@ -2078,32 +2074,32 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
     </row>
     <row r="35" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
         <v>171</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>24</v>
@@ -2113,16 +2109,16 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="C36" s="32" t="s">
+      <c r="B36" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2131,7 +2127,7 @@
         <v>173</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>27</v>
@@ -2141,16 +2137,16 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="32" t="s">
+      <c r="B38" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="18" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2159,7 +2155,7 @@
         <v>175</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>52</v>
@@ -2169,32 +2165,32 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B40" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="32" t="s">
+      <c r="B40" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
     </row>
     <row r="42" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
         <v>177</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>58</v>
@@ -2204,16 +2200,16 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="C43" s="32" t="s">
+      <c r="B43" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="18" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2222,7 +2218,7 @@
         <v>179</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>159</v>
@@ -2232,18 +2228,18 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
     </row>
     <row r="46" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>7</v>
@@ -2253,25 +2249,25 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="B47" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C47" s="32" t="s">
+      <c r="A47" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>9</v>
@@ -2282,10 +2278,10 @@
     </row>
     <row r="49" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>18</v>
@@ -2295,25 +2291,25 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="B50" s="32" t="s">
+      <c r="A50" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="B50" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C50" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="18" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="13" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>185</v>
@@ -2324,10 +2320,10 @@
     </row>
     <row r="52" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>185</v>
@@ -2337,25 +2333,25 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="B53" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C53" s="32" t="s">
+      <c r="A53" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D53" s="32" t="s">
+      <c r="D53" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>185</v>
@@ -2366,10 +2362,10 @@
     </row>
     <row r="55" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="13" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>185</v>
@@ -2379,25 +2375,25 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C56" s="32" t="s">
+      <c r="A56" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="18" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="13" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>185</v>
@@ -2411,7 +2407,7 @@
         <v>183</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>185</v>
@@ -2421,16 +2417,16 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B59" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C59" s="32" t="s">
+      <c r="B59" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="18" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2439,7 +2435,7 @@
         <v>180</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>185</v>
@@ -2453,7 +2449,7 @@
         <v>181</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>185</v>
@@ -2463,32 +2459,32 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="32" t="s">
+      <c r="A62" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B62" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C62" s="32" t="s">
+      <c r="B62" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C62" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="18" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
     </row>
     <row r="64" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="13" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>5</v>
@@ -2498,25 +2494,25 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="B65" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="C65" s="32" t="s">
+      <c r="A65" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C65" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>85</v>
@@ -2527,10 +2523,10 @@
     </row>
     <row r="67" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>85</v>
@@ -2541,10 +2537,10 @@
     </row>
     <row r="68" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>85</v>
@@ -2554,25 +2550,25 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="B69" s="32" t="s">
+      <c r="A69" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="32" t="s">
+      <c r="B69" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C69" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D69" s="32" t="s">
+      <c r="D69" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="13" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>88</v>
@@ -2583,10 +2579,10 @@
     </row>
     <row r="71" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="13" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>88</v>
@@ -2597,10 +2593,10 @@
     </row>
     <row r="72" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>88</v>
@@ -2610,25 +2606,25 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="B73" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="C73" s="32" t="s">
+      <c r="A73" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C73" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="13" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>88</v>
@@ -2638,18 +2634,18 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
     </row>
     <row r="76" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>6</v>
@@ -2659,25 +2655,25 @@
       </c>
     </row>
     <row r="77" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="B77" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="C77" s="32" t="s">
+      <c r="A77" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D77" s="32" t="s">
+      <c r="D77" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="13" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>47</v>
@@ -2688,10 +2684,10 @@
     </row>
     <row r="79" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="13" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>48</v>
@@ -2702,10 +2698,10 @@
     </row>
     <row r="80" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>49</v>
@@ -2715,18 +2711,18 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
+      <c r="B81" s="32"/>
+      <c r="C81" s="32"/>
     </row>
     <row r="82" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>34</v>
@@ -2736,25 +2732,25 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="C83" s="32" t="s">
+      <c r="A83" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C83" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D83" s="32" t="s">
+      <c r="D83" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="13" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>38</v>
@@ -2765,10 +2761,10 @@
     </row>
     <row r="85" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="13" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>62</v>
@@ -2779,10 +2775,10 @@
     </row>
     <row r="86" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="13" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>40</v>
@@ -2793,10 +2789,10 @@
     </row>
     <row r="87" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>65</v>
@@ -2806,25 +2802,25 @@
       </c>
     </row>
     <row r="88" spans="1:4" s="1" customFormat="1" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="C88" s="32" t="s">
+      <c r="A88" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C88" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D88" s="32" t="s">
+      <c r="D88" s="18" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="13" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>10</v>
@@ -2835,10 +2831,10 @@
     </row>
     <row r="90" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="13" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>20</v>
@@ -2849,10 +2845,10 @@
     </row>
     <row r="91" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="13" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>41</v>
@@ -2863,10 +2859,10 @@
     </row>
     <row r="92" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="13" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>69</v>
@@ -2876,25 +2872,25 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="B93" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="C93" s="32" t="s">
+      <c r="A93" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="32" t="s">
+      <c r="D93" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="13" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C94" s="13" t="s">
         <v>72</v>
@@ -2905,10 +2901,10 @@
     </row>
     <row r="95" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="13" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>74</v>
@@ -2919,10 +2915,10 @@
     </row>
     <row r="96" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>76</v>
@@ -2933,10 +2929,10 @@
     </row>
     <row r="97" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="13" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>78</v>
@@ -2946,25 +2942,25 @@
       </c>
     </row>
     <row r="98" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="C98" s="32" t="s">
+      <c r="A98" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D98" s="32" t="s">
+      <c r="D98" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B99" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="C99" s="13" t="s">
         <v>79</v>
@@ -3011,11 +3007,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A75:C75"/>
     <mergeCell ref="A81:C81"/>
@@ -3024,6 +3015,11 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Example/【必读】例程功能说明.xlsx
+++ b/Example/【必读】例程功能说明.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B774855-DE73-452F-BBF5-3C1F968DB65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E2D9E5-FA65-456D-ADBE-41E3E373A1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="31196" windowHeight="17038" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="252">
   <si>
     <t>文件夹名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -812,54 +812,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这个例程演示主板上显示屏接口驱动2.01寸IPS PRO显示标签控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.02寸IPS PRO显示表格控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.03寸IPS PRO显示仪表控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.04寸IPS PRO显示时钟控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.05寸IPS PRO显示进度条控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.06寸IPS PRO显示日历控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.07寸IPS PRO显示波形控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.08寸IPS PRO显示图像控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.09寸IPS PRO显示图像控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.10寸IPS PRO显示容器控件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.11寸IPS PRO显示主题1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个例程演示主板上显示屏接口驱动2.12寸IPS PRO显示主题2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E02_编码器部分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1073,6 +1025,50 @@
   </si>
   <si>
     <t>E08_图像传感器模块部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示标签控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示表格控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示仪表控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示时钟控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示进度条控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示日历控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示波形控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示图像控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示容器控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示主题1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示主题2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1341,6 +1337,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1375,12 +1377,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1698,25 +1694,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="20" x14ac:dyDescent="0.45">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
@@ -1724,11 +1720,11 @@
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="20.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
     </row>
     <row r="6" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="s">
@@ -1906,7 +1902,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>135</v>
@@ -1983,11 +1979,11 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
     </row>
     <row r="26" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
@@ -2004,11 +2000,11 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
     </row>
     <row r="28" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
@@ -2053,18 +2049,18 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
     </row>
     <row r="32" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
         <v>169</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>4</v>
@@ -2078,7 +2074,7 @@
         <v>170</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>4</v>
@@ -2088,18 +2084,18 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
     </row>
     <row r="35" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
         <v>171</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>24</v>
@@ -2113,7 +2109,7 @@
         <v>172</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>25</v>
@@ -2127,7 +2123,7 @@
         <v>173</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>27</v>
@@ -2141,7 +2137,7 @@
         <v>174</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>28</v>
@@ -2155,7 +2151,7 @@
         <v>175</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>52</v>
@@ -2169,7 +2165,7 @@
         <v>176</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>21</v>
@@ -2179,18 +2175,18 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
     </row>
     <row r="42" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
         <v>177</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>58</v>
@@ -2204,7 +2200,7 @@
         <v>178</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C43" s="18" t="s">
         <v>158</v>
@@ -2218,7 +2214,7 @@
         <v>179</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>159</v>
@@ -2228,18 +2224,18 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
     </row>
     <row r="46" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>7</v>
@@ -2250,10 +2246,10 @@
     </row>
     <row r="47" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="18" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>8</v>
@@ -2264,10 +2260,10 @@
     </row>
     <row r="48" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>9</v>
@@ -2278,10 +2274,10 @@
     </row>
     <row r="49" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="13" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>18</v>
@@ -2292,10 +2288,10 @@
     </row>
     <row r="50" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="18" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C50" s="18" t="s">
         <v>185</v>
@@ -2306,100 +2302,100 @@
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="13" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="18" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>185</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="13" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="18" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>185</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -2407,13 +2403,13 @@
         <v>183</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -2421,13 +2417,13 @@
         <v>184</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>185</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -2435,13 +2431,13 @@
         <v>180</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -2449,13 +2445,13 @@
         <v>181</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -2463,28 +2459,28 @@
         <v>182</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
     </row>
     <row r="64" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>5</v>
@@ -2495,10 +2491,10 @@
     </row>
     <row r="65" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="18" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>32</v>
@@ -2509,10 +2505,10 @@
     </row>
     <row r="66" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="13" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>85</v>
@@ -2523,10 +2519,10 @@
     </row>
     <row r="67" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="13" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>85</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="68" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="13" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>85</v>
@@ -2551,10 +2547,10 @@
     </row>
     <row r="69" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="18" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>88</v>
@@ -2565,10 +2561,10 @@
     </row>
     <row r="70" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>88</v>
@@ -2579,10 +2575,10 @@
     </row>
     <row r="71" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>88</v>
@@ -2593,10 +2589,10 @@
     </row>
     <row r="72" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="13" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>88</v>
@@ -2607,10 +2603,10 @@
     </row>
     <row r="73" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="18" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>88</v>
@@ -2621,10 +2617,10 @@
     </row>
     <row r="74" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>88</v>
@@ -2634,18 +2630,18 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="32" t="s">
+      <c r="A75" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
     </row>
     <row r="76" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>6</v>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="77" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="18" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C77" s="18" t="s">
         <v>46</v>
@@ -2670,10 +2666,10 @@
     </row>
     <row r="78" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>47</v>
@@ -2684,10 +2680,10 @@
     </row>
     <row r="79" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="13" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>48</v>
@@ -2698,10 +2694,10 @@
     </row>
     <row r="80" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="13" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>49</v>
@@ -2711,18 +2707,18 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="32" t="s">
+      <c r="A81" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B81" s="32"/>
-      <c r="C81" s="32"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
     </row>
     <row r="82" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="13" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>34</v>
@@ -2733,10 +2729,10 @@
     </row>
     <row r="83" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="18" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>36</v>
@@ -2747,10 +2743,10 @@
     </row>
     <row r="84" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="13" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>38</v>
@@ -2761,10 +2757,10 @@
     </row>
     <row r="85" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="13" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>62</v>
@@ -2775,10 +2771,10 @@
     </row>
     <row r="86" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="13" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>40</v>
@@ -2789,10 +2785,10 @@
     </row>
     <row r="87" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="13" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>65</v>
@@ -2803,10 +2799,10 @@
     </row>
     <row r="88" spans="1:4" s="1" customFormat="1" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="18" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C88" s="18" t="s">
         <v>67</v>
@@ -2817,10 +2813,10 @@
     </row>
     <row r="89" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>10</v>
@@ -2831,10 +2827,10 @@
     </row>
     <row r="90" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="13" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>20</v>
@@ -2845,10 +2841,10 @@
     </row>
     <row r="91" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>41</v>
@@ -2859,10 +2855,10 @@
     </row>
     <row r="92" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="13" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>69</v>
@@ -2873,10 +2869,10 @@
     </row>
     <row r="93" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="18" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C93" s="18" t="s">
         <v>11</v>
@@ -2887,10 +2883,10 @@
     </row>
     <row r="94" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="13" t="s">
         <v>240</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>252</v>
       </c>
       <c r="C94" s="13" t="s">
         <v>72</v>
@@ -2901,10 +2897,10 @@
     </row>
     <row r="95" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="13" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>74</v>
@@ -2915,10 +2911,10 @@
     </row>
     <row r="96" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="13" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>76</v>
@@ -2929,10 +2925,10 @@
     </row>
     <row r="97" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="13" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>78</v>
@@ -2943,10 +2939,10 @@
     </row>
     <row r="98" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="18" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>80</v>
@@ -2957,10 +2953,10 @@
     </row>
     <row r="99" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="13" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C99" s="13" t="s">
         <v>79</v>
@@ -3007,6 +3003,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A75:C75"/>
     <mergeCell ref="A81:C81"/>
@@ -3015,11 +3016,6 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Example/【必读】例程功能说明.xlsx
+++ b/Example/【必读】例程功能说明.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E2D9E5-FA65-456D-ADBE-41E3E373A1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48569607-EF77-4E29-823A-934EC5D93247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="31196" windowHeight="17038" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,82 +728,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>button_switch_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hall_stopline_detection_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>opm4a_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>encoder_quadrature_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>encoder_dir_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hip4082_single_motor_contro_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hip4082_double_motor_contro_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drv8701e_single_motor_contro_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drv8701e_double_motor_contro_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bldc_contro_demo_360c_spin27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>servo_control_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icm20602_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>imu660ra_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>imu963ra_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_container</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_theme1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_theme2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_camera_mt9v03x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_camera_scc8660</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主板2.00寸IPS PRO显示例程</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -816,190 +740,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>oled_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tft180_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips114_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_page</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_label</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_meter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_clock</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_progress_bar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_calendar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ips200pro_waveform</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wireless_uart_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bluetooth_ch9141_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_uart_udp_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_uart_tcp_client_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_uart_tcp_server_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_udp_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_tcp_client_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_oscilloscope_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_mt9v03x_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_ov7725_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wifi_spi_scc8660_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>split_ultrasonic_module_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gps_tau1201_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gps_tau1201_tft180_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gps_tau1201_ips114_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gps_tau1201_ips200_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_wireless_uart_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_bluetooth_ch9141_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_oled_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_tft180_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_ips114_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ov7725_ips200_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_wireless_uart_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_bluetooth_ch9141_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_oled_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_tft180_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_ips114_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mt9v03x_ips200_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scc8660_usbcdc_pc_mono_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scc8660_tft180_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scc8660_ips114_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scc8660_ips200_display_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>文件系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1069,6 +809,266 @@
   </si>
   <si>
     <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示主题2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1_01_button_switch_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1_02_hall_stopline_detection_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1_03_opm4a_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_01_encoder_quadrature_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_02_encoder_dir_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_01_hip4082_single_motor_contro_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_02_hip4082_double_motor_contro_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_03_drv8701e_single_motor_contro_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_04_drv8701e_double_motor_contro_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_05_bldc_contro_demo_360c_spin27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E3_06_servo_control_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_01_icm20602_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_01_oled_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_02_imu660ra_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_03_imu963ra_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_02_tft180_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_03_ips114_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_04_ips200_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_05_ips200pro_page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_06_ips200pro_label</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_07_ips200pro_table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_08_ips200pro_meter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_09_ips200pro_clock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_10_ips200pro_progress_bar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_11_ips200pro_calendar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_12_ips200pro_waveform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_13_ips200pro_camera_mt9v03x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_14_ips200pro_camera_scc8660</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_15_ips200pro_container</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_16_ips200pro_theme1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5_17_ips200pro_theme2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_01_wireless_uart_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_02_bluetooth_ch9141_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_03_wifi_uart_udp_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_04_wifi_uart_tcp_client_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_05_wifi_uart_tcp_server_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_06_wifi_spi_udp_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_07_wifi_spi_tcp_client_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_08_wifi_spi_oscilloscope_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_09_wifi_spi_mt9v03x_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_10_wifi_spi_ov7725_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E6_11_wifi_spi_scc8660_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E7_01_split_ultrasonic_module_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E7_02_gps_tau1201_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E7_03_gps_tau1201_tft180_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E7_04_gps_tau1201_ips114_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E7_05_gps_tau1201_ips200_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_02_ov7725_wireless_uart_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_03_ov7725_bluetooth_ch9141_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_04_ov7725_oled_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_05_ov7725_tft180_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_06_ov7725_ips114_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_07_ov7725_ips200_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_09_mt9v03x_wireless_uart_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_10_mt9v03x_bluetooth_ch9141_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_11_mt9v03x_oled_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_12_mt9v03x_tft180_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_13_mt9v03x_ips114_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_14_mt9v03x_ips200_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_15_scc8660_usbcdc_pc_mono_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_16_scc8660_tft180_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_17_scc8660_ips114_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_18_scc8660_ips200_display_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_01_ov7725_seekfree_assistant_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_08_mt9v03x_seekfree_assistant_demo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1902,7 +1902,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>135</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="28" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>154</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="29" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="18" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>154</v>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="30" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>154</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="32" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>4</v>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="33" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="18" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>4</v>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="35" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>24</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="36" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="18" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>25</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="37" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="13" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>27</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="38" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="18" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>28</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="39" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="13" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>52</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="40" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="18" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>21</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="42" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>58</v>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="43" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="18" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="C43" s="18" t="s">
         <v>158</v>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="44" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="13" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>159</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="46" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>7</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="47" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="18" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>8</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="48" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="13" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>9</v>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="49" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="13" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>18</v>
@@ -2288,184 +2288,184 @@
     </row>
     <row r="50" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="18" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="13" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="18" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="13" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>244</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>245</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="18" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>246</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="13" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D58" s="13" t="s">
         <v>183</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="18" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="13" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>249</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="13" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C61" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D61" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="18" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="64" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="13" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>5</v>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="65" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="18" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>32</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="66" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="13" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>85</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="67" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="13" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>85</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="68" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="13" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>85</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="69" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="18" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>88</v>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="70" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="13" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>88</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="71" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="13" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>88</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="72" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="13" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>88</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="73" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="18" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>88</v>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="74" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="13" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>88</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="76" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>6</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="77" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="18" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C77" s="18" t="s">
         <v>46</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="78" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="13" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>47</v>
@@ -2680,10 +2680,10 @@
     </row>
     <row r="79" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="13" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>48</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="80" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="13" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>49</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="82" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="13" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>34</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="83" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="18" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>36</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="84" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="13" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>38</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="85" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="13" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>62</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="86" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="13" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>40</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="87" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="13" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>65</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="88" spans="1:4" s="1" customFormat="1" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="18" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C88" s="18" t="s">
         <v>67</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="89" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="13" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="90" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="13" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>20</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="91" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="13" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>41</v>
@@ -2855,10 +2855,10 @@
     </row>
     <row r="92" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="13" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>69</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="93" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="18" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C93" s="18" t="s">
         <v>11</v>
@@ -2883,10 +2883,10 @@
     </row>
     <row r="94" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="13" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C94" s="13" t="s">
         <v>72</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="95" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="13" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>74</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="96" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="13" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>76</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="97" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="13" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>78</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="98" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="18" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>80</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="99" spans="1:4" ht="16.350000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C99" s="13" t="s">
         <v>79</v>
